--- a/02_Datasets/all_bills.xlsx
+++ b/02_Datasets/all_bills.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,156 @@
       </c>
       <c r="H2" t="n">
         <v>3.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>54781</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:55:55</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Paper Towels (Pack of 4)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>54781</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:55:55</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Basmati Rice (5kg)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>54781</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:24:30</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>70% Dark Chocolate Bar</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>54781</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:24:30</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Italian Tomato Pasta Sauce</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>54781</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:24:30</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Nutritional Health Drink (500g)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>21.9</v>
       </c>
     </row>
   </sheetData>

--- a/02_Datasets/all_bills.xlsx
+++ b/02_Datasets/all_bills.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,6 +638,36 @@
         <v>21.9</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54782</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:43:18</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Instant Noodles (Pack of 4)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_Datasets/all_bills.xlsx
+++ b/02_Datasets/all_bills.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,6 +668,186 @@
         <v>18</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>18413</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:44:27</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Horlicks Classic Malt Nutrition Drink (500g)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>295</v>
+      </c>
+      <c r="G9" t="n">
+        <v>295</v>
+      </c>
+      <c r="H9" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>18413</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:44:27</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Parle Hide &amp; Seek Choco Chip Biscuits (350g)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>75</v>
+      </c>
+      <c r="G10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H10" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>18413</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:44:27</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Britannia 100% Whole Wheat Bread (400g)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>18413</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:44:27</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fresh Hybrid Tomatoes &amp; Red Onions (2kg Pack)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>80</v>
+      </c>
+      <c r="G12" t="n">
+        <v>80</v>
+      </c>
+      <c r="H12" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>18414</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-19 11:29:16</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Suguna Farm Fresh White Eggs (Pack of 12)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>108</v>
+      </c>
+      <c r="G13" t="n">
+        <v>108</v>
+      </c>
+      <c r="H13" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18414</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-19 11:29:16</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Aashirvaad Superior MP Shudh Chakki Atta (5kg)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>270</v>
+      </c>
+      <c r="G14" t="n">
+        <v>270</v>
+      </c>
+      <c r="H14" t="n">
+        <v>378</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
